--- a/assets/翻译/en-US.xlsx
+++ b/assets/翻译/en-US.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\比较\即时战略指挥客户端\assets\翻译\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="11655"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="854">
   <si>
     <t>key</t>
   </si>
@@ -2704,6 +2709,24 @@
   </si>
   <si>
     <t>乒</t>
+  </si>
+  <si>
+    <t>Key机甲</t>
+  </si>
+  <si>
+    <t>机甲</t>
+  </si>
+  <si>
+    <t>Mech</t>
+  </si>
+  <si>
+    <t>MiaoShu_JiJia</t>
+  </si>
+  <si>
+    <t>英雄单位，杀敌获得经验升级血技能</t>
+  </si>
+  <si>
+    <t>Hero unit. Gain experience by defeating enemies to level up health and skills.</t>
   </si>
 </sst>
 </file>
@@ -3784,7 +3807,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C325"/>
+  <dimension ref="A1:C327"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="74.875" customWidth="1"/>
@@ -7366,6 +7389,28 @@
         <v>846</v>
       </c>
     </row>
+    <row r="326" spans="1:3">
+      <c r="A326" t="s">
+        <v>848</v>
+      </c>
+      <c r="B326" t="s">
+        <v>849</v>
+      </c>
+      <c r="C326" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3">
+      <c r="A327" t="s">
+        <v>851</v>
+      </c>
+      <c r="B327" t="s">
+        <v>852</v>
+      </c>
+      <c r="C327" t="s">
+        <v>853</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/assets/翻译/en-US.xlsx
+++ b/assets/翻译/en-US.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\比较\即时战略指挥客户端\assets\翻译\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UGit\cocos-creator38-demo\assets\翻译\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="864">
   <si>
     <t>key</t>
   </si>
@@ -2727,6 +2727,36 @@
   </si>
   <si>
     <t>Hero unit. Gain experience by defeating enemies to level up health and skills.</t>
+  </si>
+  <si>
+    <t>AttrName_12</t>
+  </si>
+  <si>
+    <t>火箭弹</t>
+  </si>
+  <si>
+    <t>Rocket</t>
+  </si>
+  <si>
+    <t>AttrName_13</t>
+  </si>
+  <si>
+    <t>AttrName_14</t>
+  </si>
+  <si>
+    <t>射程</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>AttrName_15</t>
+  </si>
+  <si>
+    <t>火焰</t>
+  </si>
+  <si>
+    <t>Flame</t>
   </si>
 </sst>
 </file>
@@ -3807,7 +3837,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C327"/>
+  <dimension ref="A1:C331"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="74.875" customWidth="1"/>
@@ -7411,11 +7441,55 @@
         <v>853</v>
       </c>
     </row>
+    <row r="328" spans="1:3">
+      <c r="A328" t="s">
+        <v>854</v>
+      </c>
+      <c r="B328" t="s">
+        <v>855</v>
+      </c>
+      <c r="C328" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3">
+      <c r="A329" t="s">
+        <v>857</v>
+      </c>
+      <c r="B329" t="s">
+        <v>593</v>
+      </c>
+      <c r="C329" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3">
+      <c r="A330" t="s">
+        <v>858</v>
+      </c>
+      <c r="B330" t="s">
+        <v>859</v>
+      </c>
+      <c r="C330" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3">
+      <c r="A331" t="s">
+        <v>861</v>
+      </c>
+      <c r="B331" t="s">
+        <v>862</v>
+      </c>
+      <c r="C331" t="s">
+        <v>863</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A61:C84 A154:C206 A152:C152 A142:C150 A140:C140 A138:C138 A134:C134 A136:C136 A132:C132 A130:C130 A128:C128 A126:C126 A124:C124 A122:C122 A120:C120 B114:C114 A110:C113 A118:C118 B116:C116 A90:C90 A92:C108 A1:C7 A23 A208:C227 A207:B207 A24:C59 A228:B228 A229:C229 A230:B231 A232:C310 A21:C22 A20:B20 A9:C17 A18 C18 A19:C19 A86:C88" numberStoredAsText="1"/>
+    <ignoredError sqref="A86:C88 A19:C19 C18 A18 A9:C17 A20:B20 A21:C22 A232:C310 A230:B231 A229:C229 A228:B228 A24:C59 A207:B207 A208:C227 A23 A1:C7 A92:C108 A90:C90 B116:C116 A118:C118 A110:C113 B114:C114 A120:C120 A122:C122 A124:C124 A126:C126 A128:C128 A130:C130 A132:C132 A136:C136 A134:C134 A138:C138 A140:C140 A142:C150 A152:C152 A154:C206 A61:C84" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>